--- a/CardArchive/Tools/DataExport/Effect.xlsx
+++ b/CardArchive/Tools/DataExport/Effect.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="References" sheetId="1" r:id="rId1"/>
-    <sheet name="Enums" sheetId="2" r:id="rId2"/>
-    <sheet name="Effect" sheetId="3" r:id="rId3"/>
+    <sheet name="Reference" sheetId="1" r:id="rId1"/>
+    <sheet name="Enum" sheetId="2" r:id="rId2"/>
+    <sheet name="_컬럼 설명" sheetId="3" r:id="rId3"/>
+    <sheet name="Effect" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -13,70 +14,85 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trait.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trait.xlsx</t>
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Club.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Club.xlsx</t>
+      <c r="A4"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ability.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ability.xlsx</t>
+      <c r="A5"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CardData.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CardData.xlsx</t>
+      <c r="A6"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weapon.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Weapon.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A7"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">Status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
         </is>
       </c>
     </row>
@@ -87,420 +103,1034 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectStatType</t>
-        </is>
-      </c>
-      <c r="B1"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Attack</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="G4">
         <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">HP</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="G5">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mana</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="G6">
         <v>30</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Range</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="G7">
         <v>40</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectTotalCountType</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTotalCountType</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTotalCountType</t>
+        </is>
+      </c>
+      <c r="G10">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">TotalHeal</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTotalCountType</t>
+        </is>
+      </c>
+      <c r="G11">
         <v>10</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectDamageType</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageType</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Card</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageType</t>
+        </is>
+      </c>
+      <c r="G14">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Slot</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageType</t>
+        </is>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectValueType</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="G18">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">Attack</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Health</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_PileType</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G23">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Club</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G24">
         <v>5</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Board</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G25">
         <v>10</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Hand</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G26">
         <v>20</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Deck</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G27">
         <v>30</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">Discard</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G28">
         <v>40</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Secret</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G29">
         <v>50</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">Equipped</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G30">
         <v>60</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Attached</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G31">
         <v>70</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">Temp</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G32">
         <v>90</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">PlayerAbility</t>
         </is>
       </c>
-      <c r="B32">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="G33">
         <v>100</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectStatusType</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">BadStatus</t>
         </is>
       </c>
-      <c r="B35">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="G36">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">GoodStatus</t>
         </is>
       </c>
-      <c r="B36">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">BothStatus</t>
         </is>
       </c>
-      <c r="B37">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="G38">
         <v>2</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectActionType</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">Self</t>
         </is>
       </c>
-      <c r="B40">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="G41">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">AbilityTriggerer</t>
         </is>
       </c>
-      <c r="B41">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="G42">
         <v>25</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">LastPlayed</t>
         </is>
       </c>
-      <c r="B42">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="G43">
         <v>70</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">LastTargeted</t>
         </is>
       </c>
-      <c r="B43">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="G44">
         <v>72</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t xml:space="preserve">LastSelected</t>
         </is>
       </c>
-      <c r="B44">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="G45">
         <v>74</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectPlayerType</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">All</t>
         </is>
       </c>
-      <c r="B47">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="G48">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">Player</t>
         </is>
       </c>
-      <c r="B48">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="G49">
         <v>10</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">Opponent</t>
         </is>
       </c>
-      <c r="B49">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="G50">
         <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -510,450 +1140,1378 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TableName</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect_class</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attach</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_CardData</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attacker_type</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonus_damage</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Trait</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonus_heal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Trait</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">club</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Club</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Condition</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_card</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WeightedCard[]</t>
+        </is>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_opponent</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+    </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_pile</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_type</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageType</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">direction</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlotXY</t>
+        </is>
+      </c>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effects_false</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Effect[]</t>
+        </is>
+      </c>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effects_true</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Effect[]</t>
+        </is>
+      </c>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exhausted</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gain_ability</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Ability</t>
+        </is>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">has_club</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Club</t>
+        </is>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">has_trait</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Trait</t>
+        </is>
+      </c>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+    </row>
+    <row r="25">
+      <c r="A25"/>
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">has_type</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CardType</t>
+        </is>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+    </row>
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heal_type</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+    </row>
+    <row r="27">
+      <c r="A27"/>
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">insert</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DeckInsert</t>
+        </is>
+      </c>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+    </row>
+    <row r="28">
+      <c r="A28"/>
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_same_possibility</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+    </row>
+    <row r="29">
+      <c r="A29"/>
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner_opponent</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pile</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+    </row>
+    <row r="31">
+      <c r="A31"/>
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">player</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+    </row>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">position</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlotXY</t>
+        </is>
+      </c>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+    </row>
+    <row r="33">
+      <c r="A33"/>
+      <c r="B33">
+        <v>29</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ratio</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Float</t>
+        </is>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+    </row>
+    <row r="34">
+      <c r="A34"/>
+      <c r="B34">
+        <v>30</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remove_ability</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Ability</t>
+        </is>
+      </c>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+    </row>
+    <row r="35">
+      <c r="A35"/>
+      <c r="B35">
+        <v>31</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat_type</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+    </row>
+    <row r="36">
+      <c r="A36"/>
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Status</t>
+        </is>
+      </c>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+    </row>
+    <row r="37">
+      <c r="A37"/>
+      <c r="B37">
+        <v>33</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status_type</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+    </row>
+    <row r="38">
+      <c r="A38"/>
+      <c r="B38">
+        <v>34</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target_type</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+    </row>
+    <row r="39">
+      <c r="A39"/>
+      <c r="B39">
+        <v>35</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_type</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTotalCountType</t>
+        </is>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+    </row>
+    <row r="40">
+      <c r="A40"/>
+      <c r="B40">
+        <v>36</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trait</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Trait</t>
+        </is>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+    </row>
+    <row r="41">
+      <c r="A41"/>
+      <c r="B41">
+        <v>37</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transform_to</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_CardData</t>
+        </is>
+      </c>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+    </row>
+    <row r="42">
+      <c r="A42"/>
+      <c r="B42">
+        <v>38</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+    </row>
+    <row r="43">
+      <c r="A43"/>
+      <c r="B43">
+        <v>39</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">use</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_CardData</t>
+        </is>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+    </row>
+    <row r="44">
+      <c r="A44"/>
+      <c r="B44">
+        <v>40</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">use_opponent</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+    </row>
+    <row r="45">
+      <c r="A45"/>
+      <c r="B45">
+        <v>41</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">use_stored_value</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+    </row>
+    <row r="46">
+      <c r="A46"/>
+      <c r="B46">
+        <v>42</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value_type</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+    </row>
+    <row r="47">
+      <c r="A47"/>
+      <c r="B47">
+        <v>43</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weapon</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Weapon</t>
+        </is>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+    </row>
+    <row r="48">
+      <c r="A48"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndTable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Table</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effect</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!AutoKey;!GenerateCsEnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">effect_class</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">attach</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">attacker_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">bonus_damage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">bonus_heal</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">club</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">condition</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">create_card</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">create_opponent</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">create_pile</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">damage_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">dice</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">direction</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effects_false</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effects_true</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t xml:space="preserve">exhausted</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t xml:space="preserve">gain_ability</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t xml:space="preserve">has_club</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t xml:space="preserve">has_trait</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t xml:space="preserve">has_type</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t xml:space="preserve">heal_type</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">insert</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t xml:space="preserve">is_same_possibility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t xml:space="preserve">owner_opponent</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t xml:space="preserve">pile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t xml:space="preserve">player</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">position</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t xml:space="preserve">ratio</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t xml:space="preserve">remove_ability</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t xml:space="preserve">stat_type</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t xml:space="preserve">status_type</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t xml:space="preserve">target_type</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t xml:space="preserve">total_type</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t xml:space="preserve">trait</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t xml:space="preserve">transform_to</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t xml:space="preserve">type</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t xml:space="preserve">use</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t xml:space="preserve">use_opponent</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t xml:space="preserve">use_stored_value</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t xml:space="preserve">value_type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t xml:space="preserve">weapon</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_Effect</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_CardData</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectActionType</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Trait</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Trait</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Club</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Condition</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">WeightedCard[]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_PileType</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectDamageType</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageType</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlotXY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Effect[]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_ID_Effect[]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Ability</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Club</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Trait</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_CardType</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectValueType</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_PileType</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectPlayerType</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CardType</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DeckInsert</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PileType</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlayerType</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlotXY</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Float</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Ability</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectStatType</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Status</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectStatusType</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectActionType</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectTotalCountType</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatusType</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectActionType</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTotalCountType</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Trait</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_CardData</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectStatType</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStatType</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_CardData</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_EffectValueType</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectValueType</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t xml:space="preserve">_ID_Weapon</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">add_ability_activate_burst</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectAddAbility</t>
         </is>
       </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">activate_burst</t>
-        </is>
-      </c>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
-      <c r="AI3"/>
-      <c r="AJ3"/>
-      <c r="AK3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_ability_defend_discard</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddAbility</t>
-        </is>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
@@ -969,7 +2527,11 @@
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4"/>
-      <c r="U4"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activate_burst</t>
+        </is>
+      </c>
       <c r="V4"/>
       <c r="W4"/>
       <c r="X4"/>
@@ -986,21 +2548,30 @@
       <c r="AI4"/>
       <c r="AJ4"/>
       <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_ability_play_sacrifice</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_ability_defend_discard</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectAddAbility</t>
         </is>
       </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
@@ -1033,21 +2604,30 @@
       <c r="AI5"/>
       <c r="AJ5"/>
       <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_ability_suffer_damage</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_ability_play_sacrifice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectAddAbility</t>
         </is>
       </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
       <c r="F6"/>
       <c r="G6"/>
       <c r="H6"/>
@@ -1056,11 +2636,7 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attack_suffer_damage</t>
-        </is>
-      </c>
+      <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
       <c r="Q6"/>
@@ -1084,21 +2660,30 @@
       <c r="AI6"/>
       <c r="AJ6"/>
       <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_atk_totalheal</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatTotalCount</t>
-        </is>
-      </c>
+      <c r="A7"/>
+      <c r="B7"/>
       <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_ability_suffer_damage</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddAbility</t>
+        </is>
+      </c>
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7"/>
@@ -1114,23 +2699,19 @@
       <c r="R7"/>
       <c r="S7"/>
       <c r="T7"/>
-      <c r="U7"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attack_suffer_damage</t>
+        </is>
+      </c>
       <c r="V7"/>
       <c r="W7"/>
       <c r="X7"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
+      <c r="Y7"/>
       <c r="Z7"/>
       <c r="AA7"/>
       <c r="AB7"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TotalHeal</t>
-        </is>
-      </c>
+      <c r="AC7"/>
       <c r="AD7"/>
       <c r="AE7"/>
       <c r="AF7"/>
@@ -1139,21 +2720,30 @@
       <c r="AI7"/>
       <c r="AJ7"/>
       <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_attack</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStat</t>
-        </is>
-      </c>
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_atk_totalheal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatTotalCount</t>
+        </is>
+      </c>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
@@ -1180,33 +2770,44 @@
       <c r="AC8"/>
       <c r="AD8"/>
       <c r="AE8"/>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8" t="inlineStr">
         <is>
           <t xml:space="preserve">Attack</t>
         </is>
       </c>
-      <c r="AG8"/>
-      <c r="AH8"/>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI8"/>
       <c r="AJ8"/>
       <c r="AK8"/>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TotalHeal</t>
+        </is>
+      </c>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_attack_roll</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatRoll</t>
-        </is>
-      </c>
+      <c r="A9"/>
+      <c r="B9"/>
       <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_attack</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStat</t>
+        </is>
+      </c>
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9"/>
@@ -1233,31 +2834,42 @@
       <c r="AC9"/>
       <c r="AD9"/>
       <c r="AE9"/>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
+      <c r="AF9"/>
       <c r="AG9"/>
       <c r="AH9"/>
       <c r="AI9"/>
       <c r="AJ9"/>
       <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9"/>
+      <c r="AT9"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_attack_val_CED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatCount</t>
-        </is>
-      </c>
+      <c r="A10"/>
+      <c r="B10"/>
       <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_attack_roll</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatRoll</t>
+        </is>
+      </c>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
@@ -1267,30 +2879,14 @@
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+      <c r="O10"/>
       <c r="P10"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="Q10"/>
       <c r="R10"/>
       <c r="S10"/>
       <c r="T10"/>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U10"/>
+      <c r="V10"/>
       <c r="W10"/>
       <c r="X10"/>
       <c r="Y10"/>
@@ -1300,31 +2896,40 @@
       <c r="AC10"/>
       <c r="AD10"/>
       <c r="AE10"/>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
+      <c r="AF10"/>
       <c r="AG10"/>
       <c r="AH10"/>
       <c r="AI10"/>
       <c r="AJ10"/>
       <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_club</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddClub</t>
-        </is>
-      </c>
+      <c r="A11"/>
+      <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_attack_val_CED</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatCount</t>
+        </is>
+      </c>
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -1341,15 +2946,31 @@
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11"/>
-      <c r="V11"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="W11"/>
-      <c r="X11"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y11"/>
       <c r="Z11"/>
       <c r="AA11"/>
       <c r="AB11"/>
-      <c r="AC11"/>
-      <c r="AD11"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE11"/>
       <c r="AF11"/>
       <c r="AG11"/>
@@ -1357,21 +2978,34 @@
       <c r="AI11"/>
       <c r="AJ11"/>
       <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_growth</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddTrait</t>
-        </is>
-      </c>
+      <c r="A12"/>
+      <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_club</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddClub</t>
+        </is>
+      </c>
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12"/>
@@ -1396,11 +3030,7 @@
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">growth</t>
-        </is>
-      </c>
+      <c r="AD12"/>
       <c r="AE12"/>
       <c r="AF12"/>
       <c r="AG12"/>
@@ -1408,21 +3038,30 @@
       <c r="AI12"/>
       <c r="AJ12"/>
       <c r="AK12"/>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_hp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStat</t>
-        </is>
-      </c>
+      <c r="A13"/>
+      <c r="B13"/>
       <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_growth</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddTrait</t>
+        </is>
+      </c>
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13"/>
@@ -1449,33 +3088,40 @@
       <c r="AC13"/>
       <c r="AD13"/>
       <c r="AE13"/>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HP</t>
-        </is>
-      </c>
+      <c r="AF13"/>
       <c r="AG13"/>
       <c r="AH13"/>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI13"/>
       <c r="AJ13"/>
       <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">growth</t>
+        </is>
+      </c>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_hp_totalheal</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatTotalCount</t>
-        </is>
-      </c>
+      <c r="A14"/>
+      <c r="B14"/>
       <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_hp</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStat</t>
+        </is>
+      </c>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
@@ -1495,19 +3141,11 @@
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HP</t>
-        </is>
-      </c>
+      <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
       <c r="AB14"/>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TotalHeal</t>
-        </is>
-      </c>
+      <c r="AC14"/>
       <c r="AD14"/>
       <c r="AE14"/>
       <c r="AF14"/>
@@ -1516,21 +3154,36 @@
       <c r="AI14"/>
       <c r="AJ14"/>
       <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HP</t>
+        </is>
+      </c>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14"/>
+      <c r="AT14"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_hp_val_CED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatCount</t>
-        </is>
-      </c>
+      <c r="A15"/>
+      <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_hp_totalheal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatTotalCount</t>
+        </is>
+      </c>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
@@ -1540,30 +3193,14 @@
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+      <c r="O15"/>
       <c r="P15"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="Q15"/>
       <c r="R15"/>
       <c r="S15"/>
       <c r="T15"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U15"/>
+      <c r="V15"/>
       <c r="W15"/>
       <c r="X15"/>
       <c r="Y15"/>
@@ -1573,31 +3210,44 @@
       <c r="AC15"/>
       <c r="AD15"/>
       <c r="AE15"/>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15" t="inlineStr">
         <is>
           <t xml:space="preserve">HP</t>
         </is>
       </c>
-      <c r="AG15"/>
-      <c r="AH15"/>
       <c r="AI15"/>
       <c r="AJ15"/>
       <c r="AK15"/>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TotalHeal</t>
+        </is>
+      </c>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_mana_stored</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStat</t>
-        </is>
-      </c>
+      <c r="A16"/>
+      <c r="B16"/>
       <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_hp_val_CED</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatCount</t>
+        </is>
+      </c>
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16"/>
@@ -1614,43 +3264,66 @@
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
-      <c r="V16"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="W16"/>
-      <c r="X16"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
       <c r="AB16"/>
-      <c r="AC16"/>
-      <c r="AD16"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE16"/>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mana</t>
-        </is>
-      </c>
+      <c r="AF16"/>
       <c r="AG16"/>
       <c r="AH16"/>
-      <c r="AI16" t="b">
-        <v>1</v>
-      </c>
+      <c r="AI16"/>
       <c r="AJ16"/>
       <c r="AK16"/>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HP</t>
+        </is>
+      </c>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
+      <c r="AS16"/>
+      <c r="AT16"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_mana_val_CM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddStatCount</t>
-        </is>
-      </c>
+      <c r="A17"/>
+      <c r="B17"/>
       <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_mana_stored</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStat</t>
+        </is>
+      </c>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
@@ -1661,29 +3334,13 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="P17"/>
+      <c r="Q17"/>
       <c r="R17"/>
       <c r="S17"/>
       <c r="T17"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All</t>
-        </is>
-      </c>
+      <c r="U17"/>
+      <c r="V17"/>
       <c r="W17"/>
       <c r="X17"/>
       <c r="Y17"/>
@@ -1693,31 +3350,42 @@
       <c r="AC17"/>
       <c r="AD17"/>
       <c r="AE17"/>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mana</t>
-        </is>
-      </c>
+      <c r="AF17"/>
       <c r="AG17"/>
       <c r="AH17"/>
       <c r="AI17"/>
       <c r="AJ17"/>
       <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana</t>
+        </is>
+      </c>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17">
+        <v>1</v>
+      </c>
+      <c r="AS17"/>
+      <c r="AT17"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_spell_damage</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAddTrait</t>
-        </is>
-      </c>
+      <c r="A18"/>
+      <c r="B18"/>
       <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_mana_val_CM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddStatCount</t>
+        </is>
+      </c>
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
@@ -1735,16 +3403,28 @@
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
-      <c r="W18"/>
-      <c r="X18"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
       <c r="AB18"/>
-      <c r="AC18"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage</t>
+          <t xml:space="preserve">All</t>
         </is>
       </c>
       <c r="AE18"/>
@@ -1754,21 +3434,34 @@
       <c r="AI18"/>
       <c r="AJ18"/>
       <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana</t>
+        </is>
+      </c>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attach_FL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAttachCard</t>
-        </is>
-      </c>
+      <c r="A19"/>
+      <c r="B19"/>
       <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_spell_damage</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAddTrait</t>
+        </is>
+      </c>
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
@@ -1801,25 +3494,34 @@
       <c r="AI19"/>
       <c r="AJ19"/>
       <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spell_damage</t>
+        </is>
+      </c>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
+      <c r="AS19"/>
+      <c r="AT19"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attack</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAttack</t>
-        </is>
-      </c>
+      <c r="A20"/>
+      <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Self</t>
-        </is>
-      </c>
-      <c r="E20"/>
+          <t xml:space="preserve">attach_FL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAttachCard</t>
+        </is>
+      </c>
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20"/>
@@ -1852,27 +3554,36 @@
       <c r="AI20"/>
       <c r="AJ20"/>
       <c r="AK20"/>
+      <c r="AL20"/>
+      <c r="AM20"/>
+      <c r="AN20"/>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20"/>
+      <c r="AS20"/>
+      <c r="AT20"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attack_redirect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectAttackRedirect</t>
-        </is>
-      </c>
+      <c r="A21"/>
+      <c r="B21"/>
       <c r="C21"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AbilityTriggerer</t>
-        </is>
-      </c>
-      <c r="E21"/>
+          <t xml:space="preserve">attack</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAttack</t>
+        </is>
+      </c>
       <c r="F21"/>
-      <c r="G21"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Self</t>
+        </is>
+      </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
@@ -1903,23 +3614,36 @@
       <c r="AI21"/>
       <c r="AJ21"/>
       <c r="AK21"/>
+      <c r="AL21"/>
+      <c r="AM21"/>
+      <c r="AN21"/>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21"/>
+      <c r="AS21"/>
+      <c r="AT21"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">change_MIDDLE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectChangeWeapon</t>
-        </is>
-      </c>
+      <c r="A22"/>
+      <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attack_redirect</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectAttackRedirect</t>
+        </is>
+      </c>
       <c r="F22"/>
-      <c r="G22"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AbilityTriggerer</t>
+        </is>
+      </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
@@ -1949,26 +3673,31 @@
       <c r="AH22"/>
       <c r="AI22"/>
       <c r="AJ22"/>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">change_owner_self</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectChangeOwner</t>
-        </is>
-      </c>
+      <c r="A23"/>
+      <c r="B23"/>
       <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">change_MIDDLE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectChangeWeapon</t>
+        </is>
+      </c>
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
@@ -1983,9 +3712,7 @@
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
+      <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
       <c r="W23"/>
@@ -2003,21 +3730,34 @@
       <c r="AI23"/>
       <c r="AJ23"/>
       <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clear_paralyse</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectClearStatus</t>
-        </is>
-      </c>
+      <c r="A24"/>
+      <c r="B24"/>
       <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">change_owner_self</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectChangeOwner</t>
+        </is>
+      </c>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
@@ -2038,17 +3778,11 @@
       <c r="W24"/>
       <c r="X24"/>
       <c r="Y24"/>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">paralysed</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BadStatus</t>
-        </is>
-      </c>
-      <c r="AB24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AB24">
+        <v>0</v>
+      </c>
       <c r="AC24"/>
       <c r="AD24"/>
       <c r="AE24"/>
@@ -2058,21 +3792,30 @@
       <c r="AI24"/>
       <c r="AJ24"/>
       <c r="AK24"/>
+      <c r="AL24"/>
+      <c r="AM24"/>
+      <c r="AN24"/>
+      <c r="AO24"/>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24"/>
+      <c r="AS24"/>
+      <c r="AT24"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clear_status_all</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clear_paralyse</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectClearStatus</t>
         </is>
       </c>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25"/>
@@ -2094,11 +3837,7 @@
       <c r="X25"/>
       <c r="Y25"/>
       <c r="Z25"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BadStatus</t>
-        </is>
-      </c>
+      <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25"/>
@@ -2106,24 +3845,41 @@
       <c r="AF25"/>
       <c r="AG25"/>
       <c r="AH25"/>
-      <c r="AI25"/>
-      <c r="AJ25"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paralysed</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BadStatus</t>
+        </is>
+      </c>
       <c r="AK25"/>
+      <c r="AL25"/>
+      <c r="AM25"/>
+      <c r="AN25"/>
+      <c r="AO25"/>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25"/>
+      <c r="AS25"/>
+      <c r="AT25"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clear_taunt</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clear_status_all</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectClearStatus</t>
         </is>
       </c>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26"/>
@@ -2144,16 +3900,8 @@
       <c r="W26"/>
       <c r="X26"/>
       <c r="Y26"/>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taunt</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BadStatus</t>
-        </is>
-      </c>
+      <c r="Z26"/>
+      <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26"/>
@@ -2162,23 +3910,36 @@
       <c r="AG26"/>
       <c r="AH26"/>
       <c r="AI26"/>
-      <c r="AJ26"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BadStatus</t>
+        </is>
+      </c>
       <c r="AK26"/>
+      <c r="AL26"/>
+      <c r="AM26"/>
+      <c r="AN26"/>
+      <c r="AO26"/>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26"/>
+      <c r="AS26"/>
+      <c r="AT26"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clear_temp</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectClearTemp</t>
-        </is>
-      </c>
+      <c r="A27"/>
+      <c r="B27"/>
       <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clear_stored_slot</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSetStatCustom</t>
+        </is>
+      </c>
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27"/>
@@ -2211,36 +3972,39 @@
       <c r="AI27"/>
       <c r="AJ27"/>
       <c r="AK27"/>
+      <c r="AL27"/>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored_slot</t>
+        </is>
+      </c>
+      <c r="AN27"/>
+      <c r="AO27"/>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27"/>
+      <c r="AS27"/>
+      <c r="AT27"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_dessert</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectCreateCard</t>
-        </is>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
       <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clear_taunt</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectClearStatus</t>
+        </is>
+      </c>
       <c r="F28"/>
       <c r="G28"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">card=Macaroon,weight=0.35;card=Milk,weight=0.35;card=MintChoco_Wave,weight=0.15;card=Frederica_Semla,weight=0.1;card=Miracle_5000,weight=0.05</t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hand</t>
-        </is>
-      </c>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
       <c r="M28"/>
@@ -2249,9 +4013,7 @@
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28"/>
-      <c r="S28" t="b">
-        <v>0</v>
-      </c>
+      <c r="S28"/>
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28"/>
@@ -2267,35 +4029,46 @@
       <c r="AF28"/>
       <c r="AG28"/>
       <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taunt</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BadStatus</t>
+        </is>
+      </c>
       <c r="AK28"/>
+      <c r="AL28"/>
+      <c r="AM28"/>
+      <c r="AN28"/>
+      <c r="AO28"/>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28"/>
+      <c r="AS28"/>
+      <c r="AT28"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_hand</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectCreate</t>
-        </is>
-      </c>
+      <c r="A29"/>
+      <c r="B29"/>
       <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clear_temp</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectClearTemp</t>
+        </is>
+      </c>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29"/>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hand</t>
-        </is>
-      </c>
+      <c r="I29"/>
+      <c r="J29"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29"/>
@@ -2323,47 +4096,54 @@
       <c r="AI29"/>
       <c r="AJ29"/>
       <c r="AK29"/>
+      <c r="AL29"/>
+      <c r="AM29"/>
+      <c r="AN29"/>
+      <c r="AO29"/>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29"/>
+      <c r="AS29"/>
+      <c r="AT29"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_self_HDB</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_dessert</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectCreateCard</t>
         </is>
       </c>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">card=Halo_Destroying_Bomb,weight=1</t>
-        </is>
-      </c>
-      <c r="I30" t="b">
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card=Macaroon,weight=0.35;card=Milk,weight=0.35;card=MintChoco_Wave,weight=0.15;card=Frederica_Semla,weight=0.1;card=Miracle_5000,weight=0.05</t>
+        </is>
+      </c>
+      <c r="M30">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Hand</t>
         </is>
       </c>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
       <c r="O30"/>
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
-      <c r="S30" t="b">
-        <v>1</v>
-      </c>
+      <c r="S30"/>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30"/>
@@ -2371,7 +4151,9 @@
       <c r="X30"/>
       <c r="Y30"/>
       <c r="Z30"/>
-      <c r="AA30"/>
+      <c r="AA30">
+        <v>0</v>
+      </c>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30"/>
@@ -2382,47 +4164,50 @@
       <c r="AI30"/>
       <c r="AJ30"/>
       <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
+      <c r="AS30"/>
+      <c r="AT30"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_self_SH</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectCreateCard</t>
-        </is>
-      </c>
+      <c r="A31"/>
+      <c r="B31"/>
       <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_hand</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCreate</t>
+        </is>
+      </c>
       <c r="F31"/>
       <c r="G31"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">card=Suspicious_Haniwa,weight=1</t>
-        </is>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hand</t>
-        </is>
-      </c>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
       <c r="K31"/>
       <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand</t>
+        </is>
+      </c>
       <c r="O31"/>
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31"/>
-      <c r="S31" t="b">
-        <v>1</v>
-      </c>
+      <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31"/>
@@ -2441,47 +4226,54 @@
       <c r="AI31"/>
       <c r="AJ31"/>
       <c r="AK31"/>
+      <c r="AL31"/>
+      <c r="AM31"/>
+      <c r="AN31"/>
+      <c r="AO31"/>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+      <c r="AR31"/>
+      <c r="AS31"/>
+      <c r="AT31"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_self_cafe</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_scry_keep</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectCreateCard</t>
         </is>
       </c>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">card=Cafe,weight=1</t>
-        </is>
-      </c>
-      <c r="I32" t="b">
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card=Scry_Keep,weight=1</t>
+        </is>
+      </c>
+      <c r="M32">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hand</t>
-        </is>
-      </c>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp</t>
+        </is>
+      </c>
       <c r="O32"/>
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32"/>
-      <c r="S32" t="b">
-        <v>1</v>
-      </c>
+      <c r="S32"/>
       <c r="T32"/>
       <c r="U32"/>
       <c r="V32"/>
@@ -2489,7 +4281,9 @@
       <c r="X32"/>
       <c r="Y32"/>
       <c r="Z32"/>
-      <c r="AA32"/>
+      <c r="AA32">
+        <v>1</v>
+      </c>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32"/>
@@ -2500,36 +4294,49 @@
       <c r="AI32"/>
       <c r="AJ32"/>
       <c r="AK32"/>
+      <c r="AL32"/>
+      <c r="AM32"/>
+      <c r="AN32"/>
+      <c r="AO32"/>
+      <c r="AP32"/>
+      <c r="AQ32"/>
+      <c r="AR32"/>
+      <c r="AS32"/>
+      <c r="AT32"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_temp</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectCreate</t>
-        </is>
-      </c>
+      <c r="A33"/>
+      <c r="B33"/>
       <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_self_HDB</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCreateCard</t>
+        </is>
+      </c>
       <c r="F33"/>
       <c r="G33"/>
       <c r="H33"/>
-      <c r="I33" t="b">
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card=Halo_Destroying_Bomb,weight=1</t>
+        </is>
+      </c>
+      <c r="M33">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temp</t>
-        </is>
-      </c>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand</t>
+        </is>
+      </c>
       <c r="O33"/>
       <c r="P33"/>
       <c r="Q33"/>
@@ -2542,7 +4349,9 @@
       <c r="X33"/>
       <c r="Y33"/>
       <c r="Z33"/>
-      <c r="AA33"/>
+      <c r="AA33">
+        <v>1</v>
+      </c>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33"/>
@@ -2553,30 +4362,49 @@
       <c r="AI33"/>
       <c r="AJ33"/>
       <c r="AK33"/>
+      <c r="AL33"/>
+      <c r="AM33"/>
+      <c r="AN33"/>
+      <c r="AO33"/>
+      <c r="AP33"/>
+      <c r="AQ33"/>
+      <c r="AR33"/>
+      <c r="AS33"/>
+      <c r="AT33"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_0.5</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamageRatio</t>
-        </is>
-      </c>
+      <c r="A34"/>
+      <c r="B34"/>
       <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_self_SH</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCreateCard</t>
+        </is>
+      </c>
       <c r="F34"/>
       <c r="G34"/>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card=Suspicious_Haniwa,weight=1</t>
+        </is>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand</t>
+        </is>
+      </c>
       <c r="O34"/>
       <c r="P34"/>
       <c r="Q34"/>
@@ -2585,13 +4413,13 @@
       <c r="T34"/>
       <c r="U34"/>
       <c r="V34"/>
-      <c r="W34">
-        <v>0.5</v>
-      </c>
+      <c r="W34"/>
       <c r="X34"/>
       <c r="Y34"/>
       <c r="Z34"/>
-      <c r="AA34"/>
+      <c r="AA34">
+        <v>1</v>
+      </c>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34"/>
@@ -2602,63 +4430,64 @@
       <c r="AI34"/>
       <c r="AJ34"/>
       <c r="AK34"/>
+      <c r="AL34"/>
+      <c r="AM34"/>
+      <c r="AN34"/>
+      <c r="AO34"/>
+      <c r="AP34"/>
+      <c r="AQ34"/>
+      <c r="AR34"/>
+      <c r="AS34"/>
+      <c r="AT34"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_CED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamageCount</t>
-        </is>
-      </c>
+      <c r="A35"/>
+      <c r="B35"/>
       <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_self_cafe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCreateCard</t>
+        </is>
+      </c>
       <c r="F35"/>
       <c r="G35"/>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card</t>
-        </is>
-      </c>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+      <c r="K35"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card=Cafe,weight=1</t>
+        </is>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand</t>
+        </is>
+      </c>
+      <c r="O35"/>
       <c r="P35"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="Q35"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U35"/>
+      <c r="V35"/>
       <c r="W35"/>
       <c r="X35"/>
       <c r="Y35"/>
       <c r="Z35"/>
-      <c r="AA35"/>
+      <c r="AA35">
+        <v>1</v>
+      </c>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35"/>
@@ -2669,58 +4498,53 @@
       <c r="AI35"/>
       <c r="AJ35"/>
       <c r="AK35"/>
+      <c r="AL35"/>
+      <c r="AM35"/>
+      <c r="AN35"/>
+      <c r="AO35"/>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35"/>
+      <c r="AS35"/>
+      <c r="AT35"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_CGRS</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamageCount</t>
-        </is>
-      </c>
+      <c r="A36"/>
+      <c r="B36"/>
       <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_temp</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCreate</t>
+        </is>
+      </c>
       <c r="F36"/>
       <c r="G36"/>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card</t>
-        </is>
-      </c>
+      <c r="K36"/>
       <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
-        </is>
-      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp</t>
+        </is>
+      </c>
+      <c r="O36"/>
       <c r="P36"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U36"/>
+      <c r="V36"/>
       <c r="W36"/>
       <c r="X36"/>
       <c r="Y36"/>
@@ -2736,58 +4560,47 @@
       <c r="AI36"/>
       <c r="AJ36"/>
       <c r="AK36"/>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36"/>
+      <c r="AO36"/>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36"/>
+      <c r="AS36"/>
+      <c r="AT36"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_CHSD</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamageCount</t>
-        </is>
-      </c>
+      <c r="A37"/>
+      <c r="B37"/>
       <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cycle_teaPartyHost</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectCycleStat</t>
+        </is>
+      </c>
       <c r="F37"/>
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card</t>
-        </is>
-      </c>
+      <c r="K37"/>
       <c r="L37"/>
       <c r="M37"/>
       <c r="N37"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hot_Springs_Department</t>
-        </is>
-      </c>
+      <c r="O37"/>
       <c r="P37"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
+      <c r="Q37"/>
       <c r="R37"/>
       <c r="S37"/>
       <c r="T37"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U37"/>
+      <c r="V37"/>
       <c r="W37"/>
       <c r="X37"/>
       <c r="Y37"/>
@@ -2803,23 +4616,32 @@
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea_party_host</t>
+        </is>
+      </c>
+      <c r="AN37"/>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
+      <c r="AS37"/>
+      <c r="AT37"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_card</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamage</t>
-        </is>
-      </c>
+      <c r="A38"/>
+      <c r="B38"/>
       <c r="C38"/>
-      <c r="D38"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_0.5</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage</t>
+          <t xml:space="preserve">EffectDamageRatio</t>
         </is>
       </c>
       <c r="F38"/>
@@ -2827,11 +4649,7 @@
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card</t>
-        </is>
-      </c>
+      <c r="K38"/>
       <c r="L38"/>
       <c r="M38"/>
       <c r="N38"/>
@@ -2852,33 +4670,36 @@
       <c r="AC38"/>
       <c r="AD38"/>
       <c r="AE38"/>
-      <c r="AF38"/>
+      <c r="AF38">
+        <v>0.5</v>
+      </c>
       <c r="AG38"/>
       <c r="AH38"/>
       <c r="AI38"/>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
+      <c r="AJ38"/>
       <c r="AK38"/>
+      <c r="AL38"/>
+      <c r="AM38"/>
+      <c r="AN38"/>
+      <c r="AO38"/>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+      <c r="AR38"/>
+      <c r="AS38"/>
+      <c r="AT38"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_card_atk</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamage</t>
-        </is>
-      </c>
+      <c r="A39"/>
+      <c r="B39"/>
       <c r="C39"/>
-      <c r="D39"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_CED</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage</t>
+          <t xml:space="preserve">EffectDamageCount</t>
         </is>
       </c>
       <c r="F39"/>
@@ -2886,58 +4707,75 @@
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card</t>
-        </is>
-      </c>
+      <c r="K39"/>
       <c r="L39"/>
       <c r="M39"/>
       <c r="N39"/>
-      <c r="O39"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39"/>
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39"/>
-      <c r="V39"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="W39"/>
-      <c r="X39"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y39"/>
       <c r="Z39"/>
       <c r="AA39"/>
       <c r="AB39"/>
-      <c r="AC39"/>
-      <c r="AD39"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE39"/>
       <c r="AF39"/>
       <c r="AG39"/>
       <c r="AH39"/>
       <c r="AI39"/>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
+      <c r="AJ39"/>
       <c r="AK39"/>
+      <c r="AL39"/>
+      <c r="AM39"/>
+      <c r="AN39"/>
+      <c r="AO39"/>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39"/>
+      <c r="AS39"/>
+      <c r="AT39"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">damage_slot</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDamage</t>
-        </is>
-      </c>
+      <c r="A40"/>
+      <c r="B40"/>
       <c r="C40"/>
-      <c r="D40"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_CGRS</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage</t>
+          <t xml:space="preserve">EffectDamageCount</t>
         </is>
       </c>
       <c r="F40"/>
@@ -2945,56 +4783,77 @@
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slot</t>
-        </is>
-      </c>
+      <c r="K40"/>
       <c r="L40"/>
       <c r="M40"/>
       <c r="N40"/>
-      <c r="O40"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P40"/>
       <c r="Q40"/>
       <c r="R40"/>
       <c r="S40"/>
       <c r="T40"/>
       <c r="U40"/>
-      <c r="V40"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
+        </is>
+      </c>
       <c r="W40"/>
-      <c r="X40"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
       <c r="AB40"/>
-      <c r="AC40"/>
-      <c r="AD40"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE40"/>
       <c r="AF40"/>
       <c r="AG40"/>
       <c r="AH40"/>
       <c r="AI40"/>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
+      <c r="AJ40"/>
       <c r="AK40"/>
+      <c r="AL40"/>
+      <c r="AM40"/>
+      <c r="AN40"/>
+      <c r="AO40"/>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+      <c r="AR40"/>
+      <c r="AS40"/>
+      <c r="AT40"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">destroy</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDestroy</t>
-        </is>
-      </c>
+      <c r="A41"/>
+      <c r="B41"/>
       <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_CHSD</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamageCount</t>
+        </is>
+      </c>
       <c r="F41"/>
       <c r="G41"/>
       <c r="H41"/>
@@ -3004,22 +4863,42 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
-      <c r="O41"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41"/>
       <c r="S41"/>
       <c r="T41"/>
       <c r="U41"/>
-      <c r="V41"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hot_Springs_Department</t>
+        </is>
+      </c>
       <c r="W41"/>
-      <c r="X41"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y41"/>
       <c r="Z41"/>
       <c r="AA41"/>
       <c r="AB41"/>
-      <c r="AC41"/>
-      <c r="AD41"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE41"/>
       <c r="AF41"/>
       <c r="AG41"/>
@@ -3027,31 +4906,48 @@
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41"/>
+      <c r="AL41"/>
+      <c r="AM41"/>
+      <c r="AN41"/>
+      <c r="AO41"/>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41"/>
+      <c r="AS41"/>
+      <c r="AT41"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">destroy_equip</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDestroyEquip</t>
-        </is>
-      </c>
+      <c r="A42"/>
+      <c r="B42"/>
       <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_card</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamage</t>
+        </is>
+      </c>
       <c r="F42"/>
       <c r="G42"/>
-      <c r="H42"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spell_damage</t>
+        </is>
+      </c>
       <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
       <c r="M42"/>
       <c r="N42"/>
-      <c r="O42"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P42"/>
       <c r="Q42"/>
       <c r="R42"/>
@@ -3074,31 +4970,52 @@
       <c r="AI42"/>
       <c r="AJ42"/>
       <c r="AK42"/>
+      <c r="AL42"/>
+      <c r="AM42"/>
+      <c r="AN42"/>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="AT42"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">discard</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDiscard</t>
-        </is>
-      </c>
+      <c r="A43"/>
+      <c r="B43"/>
       <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_card_atk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamage</t>
+        </is>
+      </c>
       <c r="F43"/>
       <c r="G43"/>
-      <c r="H43"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spell_damage</t>
+        </is>
+      </c>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
       <c r="M43"/>
       <c r="N43"/>
-      <c r="O43"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P43"/>
       <c r="Q43"/>
       <c r="R43"/>
@@ -3121,31 +5038,52 @@
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43"/>
+      <c r="AL43"/>
+      <c r="AM43"/>
+      <c r="AN43"/>
+      <c r="AO43"/>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+      <c r="AR43"/>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="AT43"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">draw</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectDraw</t>
-        </is>
-      </c>
+      <c r="A44"/>
+      <c r="B44"/>
       <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_slot</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamage</t>
+        </is>
+      </c>
       <c r="F44"/>
       <c r="G44"/>
-      <c r="H44"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spell_damage</t>
+        </is>
+      </c>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
       <c r="M44"/>
       <c r="N44"/>
-      <c r="O44"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slot</t>
+        </is>
+      </c>
       <c r="P44"/>
       <c r="Q44"/>
       <c r="R44"/>
@@ -3168,21 +5106,34 @@
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44"/>
+      <c r="AL44"/>
+      <c r="AM44"/>
+      <c r="AN44"/>
+      <c r="AO44"/>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44"/>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="AT44"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exhaust</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectExhaust</t>
-        </is>
-      </c>
+      <c r="A45"/>
+      <c r="B45"/>
       <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage_stored_slot</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDamage</t>
+        </is>
+      </c>
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
@@ -3190,11 +5141,13 @@
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
-      <c r="M45" t="b">
-        <v>1</v>
-      </c>
+      <c r="M45"/>
       <c r="N45"/>
-      <c r="O45"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card</t>
+        </is>
+      </c>
       <c r="P45"/>
       <c r="Q45"/>
       <c r="R45"/>
@@ -3217,21 +5170,34 @@
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45"/>
+      <c r="AL45"/>
+      <c r="AM45"/>
+      <c r="AN45"/>
+      <c r="AO45"/>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+      <c r="AR45"/>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="AT45"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gain_mana</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectMana</t>
-        </is>
-      </c>
+      <c r="A46"/>
+      <c r="B46"/>
       <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decktop_to_bottom</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectMovePileTopToBottom</t>
+        </is>
+      </c>
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
@@ -3255,7 +5221,11 @@
       <c r="Z46"/>
       <c r="AA46"/>
       <c r="AB46"/>
-      <c r="AC46"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deck</t>
+        </is>
+      </c>
       <c r="AD46"/>
       <c r="AE46"/>
       <c r="AF46"/>
@@ -3264,21 +5234,30 @@
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46"/>
+      <c r="AL46"/>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
+      <c r="AS46"/>
+      <c r="AT46"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heal</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectHeal</t>
-        </is>
-      </c>
+      <c r="A47"/>
+      <c r="B47"/>
       <c r="C47"/>
-      <c r="D47"/>
-      <c r="E47"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">destroy</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDestroy</t>
+        </is>
+      </c>
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47"/>
@@ -3291,11 +5270,7 @@
       <c r="O47"/>
       <c r="P47"/>
       <c r="Q47"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
+      <c r="R47"/>
       <c r="S47"/>
       <c r="T47"/>
       <c r="U47"/>
@@ -3315,21 +5290,30 @@
       <c r="AI47"/>
       <c r="AJ47"/>
       <c r="AK47"/>
+      <c r="AL47"/>
+      <c r="AM47"/>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
+      <c r="AS47"/>
+      <c r="AT47"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heal_atk</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectHeal</t>
-        </is>
-      </c>
+      <c r="A48"/>
+      <c r="B48"/>
       <c r="C48"/>
-      <c r="D48"/>
-      <c r="E48"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">destroy_equip</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDestroyEquip</t>
+        </is>
+      </c>
       <c r="F48"/>
       <c r="G48"/>
       <c r="H48"/>
@@ -3342,11 +5326,7 @@
       <c r="O48"/>
       <c r="P48"/>
       <c r="Q48"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
+      <c r="R48"/>
       <c r="S48"/>
       <c r="T48"/>
       <c r="U48"/>
@@ -3366,21 +5346,30 @@
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48"/>
+      <c r="AL48"/>
+      <c r="AM48"/>
+      <c r="AN48"/>
+      <c r="AO48"/>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48"/>
+      <c r="AS48"/>
+      <c r="AT48"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">move_lt_unit</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectMoveUnit</t>
-        </is>
-      </c>
+      <c r="A49"/>
+      <c r="B49"/>
       <c r="C49"/>
-      <c r="D49"/>
-      <c r="E49"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">discard</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDiscard</t>
+        </is>
+      </c>
       <c r="F49"/>
       <c r="G49"/>
       <c r="H49"/>
@@ -3403,11 +5392,7 @@
       <c r="Y49"/>
       <c r="Z49"/>
       <c r="AA49"/>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LastTargeted</t>
-        </is>
-      </c>
+      <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -3417,21 +5402,30 @@
       <c r="AI49"/>
       <c r="AJ49"/>
       <c r="AK49"/>
+      <c r="AL49"/>
+      <c r="AM49"/>
+      <c r="AN49"/>
+      <c r="AO49"/>
+      <c r="AP49"/>
+      <c r="AQ49"/>
+      <c r="AR49"/>
+      <c r="AS49"/>
+      <c r="AT49"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">move_unit</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectMoveUnit</t>
-        </is>
-      </c>
+      <c r="A50"/>
+      <c r="B50"/>
       <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">draw</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectDraw</t>
+        </is>
+      </c>
       <c r="F50"/>
       <c r="G50"/>
       <c r="H50"/>
@@ -3454,11 +5448,7 @@
       <c r="Y50"/>
       <c r="Z50"/>
       <c r="AA50"/>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Self</t>
-        </is>
-      </c>
+      <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50"/>
       <c r="AE50"/>
@@ -3468,21 +5458,30 @@
       <c r="AI50"/>
       <c r="AJ50"/>
       <c r="AK50"/>
+      <c r="AL50"/>
+      <c r="AM50"/>
+      <c r="AN50"/>
+      <c r="AO50"/>
+      <c r="AP50"/>
+      <c r="AQ50"/>
+      <c r="AR50"/>
+      <c r="AS50"/>
+      <c r="AT50"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">play_card</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectPlay</t>
-        </is>
-      </c>
+      <c r="A51"/>
+      <c r="B51"/>
       <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exhaust</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectExhaust</t>
+        </is>
+      </c>
       <c r="F51"/>
       <c r="G51"/>
       <c r="H51"/>
@@ -3497,7 +5496,9 @@
       <c r="Q51"/>
       <c r="R51"/>
       <c r="S51"/>
-      <c r="T51"/>
+      <c r="T51">
+        <v>1</v>
+      </c>
       <c r="U51"/>
       <c r="V51"/>
       <c r="W51"/>
@@ -3515,21 +5516,30 @@
       <c r="AI51"/>
       <c r="AJ51"/>
       <c r="AK51"/>
+      <c r="AL51"/>
+      <c r="AM51"/>
+      <c r="AN51"/>
+      <c r="AO51"/>
+      <c r="AP51"/>
+      <c r="AQ51"/>
+      <c r="AR51"/>
+      <c r="AS51"/>
+      <c r="AT51"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">remove_ability_aura_help</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectRemoveAbility</t>
-        </is>
-      </c>
+      <c r="A52"/>
+      <c r="B52"/>
       <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gain_mana</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectMana</t>
+        </is>
+      </c>
       <c r="F52"/>
       <c r="G52"/>
       <c r="H52"/>
@@ -3562,21 +5572,30 @@
       <c r="AI52"/>
       <c r="AJ52"/>
       <c r="AK52"/>
+      <c r="AL52"/>
+      <c r="AM52"/>
+      <c r="AN52"/>
+      <c r="AO52"/>
+      <c r="AP52"/>
+      <c r="AQ52"/>
+      <c r="AR52"/>
+      <c r="AS52"/>
+      <c r="AT52"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">remove_all_bad_status</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectClearStatus</t>
-        </is>
-      </c>
+      <c r="A53"/>
+      <c r="B53"/>
       <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heal</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectHeal</t>
+        </is>
+      </c>
       <c r="F53"/>
       <c r="G53"/>
       <c r="H53"/>
@@ -3596,13 +5615,13 @@
       <c r="V53"/>
       <c r="W53"/>
       <c r="X53"/>
-      <c r="Y53"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
       <c r="Z53"/>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BadStatus</t>
-        </is>
-      </c>
+      <c r="AA53"/>
       <c r="AB53"/>
       <c r="AC53"/>
       <c r="AD53"/>
@@ -3613,21 +5632,30 @@
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53"/>
+      <c r="AL53"/>
+      <c r="AM53"/>
+      <c r="AN53"/>
+      <c r="AO53"/>
+      <c r="AP53"/>
+      <c r="AQ53"/>
+      <c r="AR53"/>
+      <c r="AS53"/>
+      <c r="AT53"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reset_stats</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectResetStat</t>
-        </is>
-      </c>
+      <c r="A54"/>
+      <c r="B54"/>
       <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heal_atk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectHeal</t>
+        </is>
+      </c>
       <c r="F54"/>
       <c r="G54"/>
       <c r="H54"/>
@@ -3647,7 +5675,11 @@
       <c r="V54"/>
       <c r="W54"/>
       <c r="X54"/>
-      <c r="Y54"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
       <c r="Z54"/>
       <c r="AA54"/>
       <c r="AB54"/>
@@ -3660,37 +5692,52 @@
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54"/>
+      <c r="AL54"/>
+      <c r="AM54"/>
+      <c r="AN54"/>
+      <c r="AO54"/>
+      <c r="AP54"/>
+      <c r="AQ54"/>
+      <c r="AR54"/>
+      <c r="AS54"/>
+      <c r="AT54"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roll_d6</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectRoll</t>
-        </is>
-      </c>
+      <c r="A55"/>
+      <c r="B55"/>
       <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mika_atk_if</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectConditional</t>
+        </is>
+      </c>
       <c r="F55"/>
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55">
-        <v>6</v>
-      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_Mika</t>
+        </is>
+      </c>
+      <c r="L55"/>
       <c r="M55"/>
       <c r="N55"/>
       <c r="O55"/>
       <c r="P55"/>
       <c r="Q55"/>
       <c r="R55"/>
-      <c r="S55"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_attack</t>
+        </is>
+      </c>
       <c r="T55"/>
       <c r="U55"/>
       <c r="V55"/>
@@ -3709,21 +5756,30 @@
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55"/>
+      <c r="AL55"/>
+      <c r="AM55"/>
+      <c r="AN55"/>
+      <c r="AO55"/>
+      <c r="AP55"/>
+      <c r="AQ55"/>
+      <c r="AR55"/>
+      <c r="AS55"/>
+      <c r="AT55"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">send_deck</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSendPile</t>
-        </is>
-      </c>
+      <c r="A56"/>
+      <c r="B56"/>
       <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">move_lt_unit</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectMoveUnit</t>
+        </is>
+      </c>
       <c r="F56"/>
       <c r="G56"/>
       <c r="H56"/>
@@ -3739,11 +5795,7 @@
       <c r="R56"/>
       <c r="S56"/>
       <c r="T56"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deck</t>
-        </is>
-      </c>
+      <c r="U56"/>
       <c r="V56"/>
       <c r="W56"/>
       <c r="X56"/>
@@ -3759,22 +5811,35 @@
       <c r="AH56"/>
       <c r="AI56"/>
       <c r="AJ56"/>
-      <c r="AK56"/>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LastTargeted</t>
+        </is>
+      </c>
+      <c r="AL56"/>
+      <c r="AM56"/>
+      <c r="AN56"/>
+      <c r="AO56"/>
+      <c r="AP56"/>
+      <c r="AQ56"/>
+      <c r="AR56"/>
+      <c r="AS56"/>
+      <c r="AT56"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">send_hand</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSendPile</t>
-        </is>
-      </c>
+      <c r="A57"/>
+      <c r="B57"/>
       <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">move_unit</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectMoveUnit</t>
+        </is>
+      </c>
       <c r="F57"/>
       <c r="G57"/>
       <c r="H57"/>
@@ -3790,11 +5855,7 @@
       <c r="R57"/>
       <c r="S57"/>
       <c r="T57"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hand</t>
-        </is>
-      </c>
+      <c r="U57"/>
       <c r="V57"/>
       <c r="W57"/>
       <c r="X57"/>
@@ -3810,22 +5871,35 @@
       <c r="AH57"/>
       <c r="AI57"/>
       <c r="AJ57"/>
-      <c r="AK57"/>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Self</t>
+        </is>
+      </c>
+      <c r="AL57"/>
+      <c r="AM57"/>
+      <c r="AN57"/>
+      <c r="AO57"/>
+      <c r="AP57"/>
+      <c r="AQ57"/>
+      <c r="AR57"/>
+      <c r="AS57"/>
+      <c r="AT57"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">set_attack</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSetStat</t>
-        </is>
-      </c>
+      <c r="A58"/>
+      <c r="B58"/>
       <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">play_card</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectPlay</t>
+        </is>
+      </c>
       <c r="F58"/>
       <c r="G58"/>
       <c r="H58"/>
@@ -3852,31 +5926,36 @@
       <c r="AC58"/>
       <c r="AD58"/>
       <c r="AE58"/>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
+      <c r="AF58"/>
       <c r="AG58"/>
       <c r="AH58"/>
       <c r="AI58"/>
       <c r="AJ58"/>
       <c r="AK58"/>
+      <c r="AL58"/>
+      <c r="AM58"/>
+      <c r="AN58"/>
+      <c r="AO58"/>
+      <c r="AP58"/>
+      <c r="AQ58"/>
+      <c r="AR58"/>
+      <c r="AS58"/>
+      <c r="AT58"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">set_club_ui</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSetClubCardUI</t>
-        </is>
-      </c>
+      <c r="A59"/>
+      <c r="B59"/>
       <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remove_ability_aura_help</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectRemoveAbility</t>
+        </is>
+      </c>
       <c r="F59"/>
       <c r="G59"/>
       <c r="H59"/>
@@ -3909,21 +5988,30 @@
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59"/>
+      <c r="AL59"/>
+      <c r="AM59"/>
+      <c r="AN59"/>
+      <c r="AO59"/>
+      <c r="AP59"/>
+      <c r="AQ59"/>
+      <c r="AR59"/>
+      <c r="AS59"/>
+      <c r="AT59"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">set_hp</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSetStat</t>
-        </is>
-      </c>
+      <c r="A60"/>
+      <c r="B60"/>
       <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remove_all_bad_status</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectClearStatus</t>
+        </is>
+      </c>
       <c r="F60"/>
       <c r="G60"/>
       <c r="H60"/>
@@ -3950,31 +6038,40 @@
       <c r="AC60"/>
       <c r="AD60"/>
       <c r="AE60"/>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HP</t>
-        </is>
-      </c>
+      <c r="AF60"/>
       <c r="AG60"/>
       <c r="AH60"/>
       <c r="AI60"/>
-      <c r="AJ60"/>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BadStatus</t>
+        </is>
+      </c>
       <c r="AK60"/>
+      <c r="AL60"/>
+      <c r="AM60"/>
+      <c r="AN60"/>
+      <c r="AO60"/>
+      <c r="AP60"/>
+      <c r="AQ60"/>
+      <c r="AR60"/>
+      <c r="AS60"/>
+      <c r="AT60"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">set_mana</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectSetStat</t>
-        </is>
-      </c>
+      <c r="A61"/>
+      <c r="B61"/>
       <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reset_stats</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectResetStat</t>
+        </is>
+      </c>
       <c r="F61"/>
       <c r="G61"/>
       <c r="H61"/>
@@ -4001,31 +6098,36 @@
       <c r="AC61"/>
       <c r="AD61"/>
       <c r="AE61"/>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mana</t>
-        </is>
-      </c>
+      <c r="AF61"/>
       <c r="AG61"/>
       <c r="AH61"/>
       <c r="AI61"/>
       <c r="AJ61"/>
       <c r="AK61"/>
+      <c r="AL61"/>
+      <c r="AM61"/>
+      <c r="AN61"/>
+      <c r="AO61"/>
+      <c r="AP61"/>
+      <c r="AQ61"/>
+      <c r="AR61"/>
+      <c r="AS61"/>
+      <c r="AT61"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shuffle_deck</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectShuffle</t>
-        </is>
-      </c>
+      <c r="A62"/>
+      <c r="B62"/>
       <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roll_d6</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectRoll</t>
+        </is>
+      </c>
       <c r="F62"/>
       <c r="G62"/>
       <c r="H62"/>
@@ -4036,7 +6138,9 @@
       <c r="M62"/>
       <c r="N62"/>
       <c r="O62"/>
-      <c r="P62"/>
+      <c r="P62">
+        <v>6</v>
+      </c>
       <c r="Q62"/>
       <c r="R62"/>
       <c r="S62"/>
@@ -4058,54 +6162,55 @@
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62"/>
+      <c r="AL62"/>
+      <c r="AM62"/>
+      <c r="AN62"/>
+      <c r="AO62"/>
+      <c r="AP62"/>
+      <c r="AQ62"/>
+      <c r="AR62"/>
+      <c r="AS62"/>
+      <c r="AT62"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_val_CM</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectStoreCount</t>
-        </is>
-      </c>
+      <c r="A63"/>
+      <c r="B63"/>
       <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scry_branch</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectConditional</t>
+        </is>
+      </c>
       <c r="F63"/>
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
       <c r="J63"/>
-      <c r="K63"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pilepos_deck_top</t>
+        </is>
+      </c>
       <c r="L63"/>
       <c r="M63"/>
       <c r="N63"/>
       <c r="O63"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="R63"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decktop_to_bottom</t>
+        </is>
+      </c>
       <c r="S63"/>
       <c r="T63"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Board</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player</t>
-        </is>
-      </c>
+      <c r="U63"/>
+      <c r="V63"/>
       <c r="W63"/>
       <c r="X63"/>
       <c r="Y63"/>
@@ -4121,21 +6226,30 @@
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63"/>
+      <c r="AL63"/>
+      <c r="AM63"/>
+      <c r="AN63"/>
+      <c r="AO63"/>
+      <c r="AP63"/>
+      <c r="AQ63"/>
+      <c r="AR63"/>
+      <c r="AS63"/>
+      <c r="AT63"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_ASSC</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A64"/>
+      <c r="B64"/>
       <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">send_deck</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSendPile</t>
+        </is>
+      </c>
       <c r="F64"/>
       <c r="G64"/>
       <c r="H64"/>
@@ -4156,35 +6270,50 @@
       <c r="W64"/>
       <c r="X64"/>
       <c r="Y64"/>
-      <c r="Z64"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottom</t>
+        </is>
+      </c>
       <c r="AA64"/>
       <c r="AB64"/>
-      <c r="AC64"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deck</t>
+        </is>
+      </c>
       <c r="AD64"/>
       <c r="AE64"/>
       <c r="AF64"/>
       <c r="AG64"/>
-      <c r="AH64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AH64"/>
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64"/>
+      <c r="AL64"/>
+      <c r="AM64"/>
+      <c r="AN64"/>
+      <c r="AO64"/>
+      <c r="AP64"/>
+      <c r="AQ64"/>
+      <c r="AR64"/>
+      <c r="AS64"/>
+      <c r="AT64"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_CT</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A65"/>
+      <c r="B65"/>
       <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">send_hand</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSendPile</t>
+        </is>
+      </c>
       <c r="F65"/>
       <c r="G65"/>
       <c r="H65"/>
@@ -4205,39 +6334,50 @@
       <c r="W65"/>
       <c r="X65"/>
       <c r="Y65"/>
-      <c r="Z65"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottom</t>
+        </is>
+      </c>
       <c r="AA65"/>
       <c r="AB65"/>
-      <c r="AC65"/>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hand</t>
+        </is>
+      </c>
       <c r="AD65"/>
       <c r="AE65"/>
       <c r="AF65"/>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Catering_Truck</t>
-        </is>
-      </c>
-      <c r="AH65" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG65"/>
+      <c r="AH65"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65"/>
+      <c r="AL65"/>
+      <c r="AM65"/>
+      <c r="AN65"/>
+      <c r="AO65"/>
+      <c r="AP65"/>
+      <c r="AQ65"/>
+      <c r="AR65"/>
+      <c r="AS65"/>
+      <c r="AT65"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_HS</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A66"/>
+      <c r="B66"/>
       <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">set_attack</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSetStat</t>
+        </is>
+      </c>
       <c r="F66"/>
       <c r="G66"/>
       <c r="H66"/>
@@ -4265,32 +6405,39 @@
       <c r="AD66"/>
       <c r="AE66"/>
       <c r="AF66"/>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hot_Spring</t>
-        </is>
-      </c>
-      <c r="AH66" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG66"/>
+      <c r="AH66"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66"/>
+      <c r="AL66"/>
+      <c r="AM66"/>
+      <c r="AN66"/>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="AP66"/>
+      <c r="AQ66"/>
+      <c r="AR66"/>
+      <c r="AS66"/>
+      <c r="AT66"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_JTFM</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A67"/>
+      <c r="B67"/>
       <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">set_club_ui</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSetClubCardUI</t>
+        </is>
+      </c>
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67"/>
@@ -4318,32 +6465,35 @@
       <c r="AD67"/>
       <c r="AE67"/>
       <c r="AF67"/>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Justice_Task_Force_Memeber</t>
-        </is>
-      </c>
-      <c r="AH67" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG67"/>
+      <c r="AH67"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67"/>
+      <c r="AL67"/>
+      <c r="AM67"/>
+      <c r="AN67"/>
+      <c r="AO67"/>
+      <c r="AP67"/>
+      <c r="AQ67"/>
+      <c r="AR67"/>
+      <c r="AS67"/>
+      <c r="AT67"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_KD</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A68"/>
+      <c r="B68"/>
       <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">set_hp</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSetStat</t>
+        </is>
+      </c>
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68"/>
@@ -4371,32 +6521,39 @@
       <c r="AD68"/>
       <c r="AE68"/>
       <c r="AF68"/>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kaiser_PMC_Drone</t>
-        </is>
-      </c>
-      <c r="AH68" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG68"/>
+      <c r="AH68"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68"/>
+      <c r="AL68"/>
+      <c r="AM68"/>
+      <c r="AN68"/>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HP</t>
+        </is>
+      </c>
+      <c r="AP68"/>
+      <c r="AQ68"/>
+      <c r="AR68"/>
+      <c r="AS68"/>
+      <c r="AT68"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_PZ</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A69"/>
+      <c r="B69"/>
       <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">set_mana</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSetStat</t>
+        </is>
+      </c>
       <c r="F69"/>
       <c r="G69"/>
       <c r="H69"/>
@@ -4424,32 +6581,39 @@
       <c r="AD69"/>
       <c r="AE69"/>
       <c r="AF69"/>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pan_Zzang</t>
-        </is>
-      </c>
-      <c r="AH69" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG69"/>
+      <c r="AH69"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69"/>
+      <c r="AL69"/>
+      <c r="AM69"/>
+      <c r="AN69"/>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana</t>
+        </is>
+      </c>
+      <c r="AP69"/>
+      <c r="AQ69"/>
+      <c r="AR69"/>
+      <c r="AS69"/>
+      <c r="AT69"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_SSRFS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A70"/>
+      <c r="B70"/>
       <c r="C70"/>
-      <c r="D70"/>
-      <c r="E70"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shuffle_deck</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectShuffle</t>
+        </is>
+      </c>
       <c r="F70"/>
       <c r="G70"/>
       <c r="H70"/>
@@ -4477,32 +6641,35 @@
       <c r="AD70"/>
       <c r="AE70"/>
       <c r="AF70"/>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall</t>
-        </is>
-      </c>
-      <c r="AH70" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG70"/>
+      <c r="AH70"/>
       <c r="AI70"/>
       <c r="AJ70"/>
       <c r="AK70"/>
+      <c r="AL70"/>
+      <c r="AM70"/>
+      <c r="AN70"/>
+      <c r="AO70"/>
+      <c r="AP70"/>
+      <c r="AQ70"/>
+      <c r="AR70"/>
+      <c r="AS70"/>
+      <c r="AT70"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_peroro</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A71"/>
+      <c r="B71"/>
       <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_val_CM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectStoreCount</t>
+        </is>
+      </c>
       <c r="F71"/>
       <c r="G71"/>
       <c r="H71"/>
@@ -4520,42 +6687,61 @@
       <c r="T71"/>
       <c r="U71"/>
       <c r="V71"/>
-      <c r="W71"/>
-      <c r="X71"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
       <c r="Y71"/>
       <c r="Z71"/>
       <c r="AA71"/>
       <c r="AB71"/>
-      <c r="AC71"/>
-      <c r="AD71"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Board</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player</t>
+        </is>
+      </c>
       <c r="AE71"/>
       <c r="AF71"/>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peroro_Tlush</t>
-        </is>
-      </c>
-      <c r="AH71" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG71"/>
+      <c r="AH71"/>
       <c r="AI71"/>
       <c r="AJ71"/>
       <c r="AK71"/>
+      <c r="AL71"/>
+      <c r="AM71"/>
+      <c r="AN71"/>
+      <c r="AO71"/>
+      <c r="AP71"/>
+      <c r="AQ71"/>
+      <c r="AR71"/>
+      <c r="AS71"/>
+      <c r="AT71"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_sweeper</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectUseCard</t>
-        </is>
-      </c>
+      <c r="A72"/>
+      <c r="B72"/>
       <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_22_x_inc</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectSummonSlot</t>
+        </is>
+      </c>
       <c r="F72"/>
       <c r="G72"/>
       <c r="H72"/>
@@ -4567,7 +6753,11 @@
       <c r="N72"/>
       <c r="O72"/>
       <c r="P72"/>
-      <c r="Q72"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x=1,y=0</t>
+        </is>
+      </c>
       <c r="R72"/>
       <c r="S72"/>
       <c r="T72"/>
@@ -4581,34 +6771,41 @@
       <c r="AB72"/>
       <c r="AC72"/>
       <c r="AD72"/>
-      <c r="AE72"/>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x=2,y=2</t>
+        </is>
+      </c>
       <c r="AF72"/>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sweeper</t>
-        </is>
-      </c>
-      <c r="AH72" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG72"/>
+      <c r="AH72"/>
       <c r="AI72"/>
       <c r="AJ72"/>
       <c r="AK72"/>
+      <c r="AL72"/>
+      <c r="AM72"/>
+      <c r="AN72"/>
+      <c r="AO72"/>
+      <c r="AP72"/>
+      <c r="AQ72"/>
+      <c r="AR72"/>
+      <c r="AS72"/>
+      <c r="AT72"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_sweeper_Tutorial</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_ASSC</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectUseCard</t>
         </is>
       </c>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73"/>
       <c r="F73"/>
       <c r="G73"/>
       <c r="H73"/>
@@ -4636,32 +6833,37 @@
       <c r="AD73"/>
       <c r="AE73"/>
       <c r="AF73"/>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sweeper_Tutorial</t>
-        </is>
-      </c>
-      <c r="AH73" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG73"/>
+      <c r="AH73"/>
       <c r="AI73"/>
       <c r="AJ73"/>
       <c r="AK73"/>
+      <c r="AL73"/>
+      <c r="AM73"/>
+      <c r="AN73"/>
+      <c r="AO73"/>
+      <c r="AP73"/>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73"/>
+      <c r="AS73"/>
+      <c r="AT73"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_thundergun</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_CT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectUseCard</t>
         </is>
       </c>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
       <c r="F74"/>
       <c r="G74"/>
       <c r="H74"/>
@@ -4689,32 +6891,41 @@
       <c r="AD74"/>
       <c r="AE74"/>
       <c r="AF74"/>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thundergun</t>
-        </is>
-      </c>
-      <c r="AH74" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG74"/>
+      <c r="AH74"/>
       <c r="AI74"/>
       <c r="AJ74"/>
       <c r="AK74"/>
+      <c r="AL74"/>
+      <c r="AM74"/>
+      <c r="AN74"/>
+      <c r="AO74"/>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catering_Truck</t>
+        </is>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74"/>
+      <c r="AS74"/>
+      <c r="AT74"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summon_thundergun_Tutorial</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_HS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectUseCard</t>
         </is>
       </c>
-      <c r="C75"/>
-      <c r="D75"/>
-      <c r="E75"/>
       <c r="F75"/>
       <c r="G75"/>
       <c r="H75"/>
@@ -4742,32 +6953,41 @@
       <c r="AD75"/>
       <c r="AE75"/>
       <c r="AF75"/>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thundergun_Tutorial</t>
-        </is>
-      </c>
-      <c r="AH75" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG75"/>
+      <c r="AH75"/>
       <c r="AI75"/>
       <c r="AJ75"/>
       <c r="AK75"/>
+      <c r="AL75"/>
+      <c r="AM75"/>
+      <c r="AN75"/>
+      <c r="AO75"/>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hot_Spring</t>
+        </is>
+      </c>
+      <c r="AQ75">
+        <v>1</v>
+      </c>
+      <c r="AR75"/>
+      <c r="AS75"/>
+      <c r="AT75"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transform_fish</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectTransform</t>
-        </is>
-      </c>
+      <c r="A76"/>
+      <c r="B76"/>
       <c r="C76"/>
-      <c r="D76"/>
-      <c r="E76"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_JTFM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76"/>
@@ -4800,21 +7020,36 @@
       <c r="AI76"/>
       <c r="AJ76"/>
       <c r="AK76"/>
+      <c r="AL76"/>
+      <c r="AM76"/>
+      <c r="AN76"/>
+      <c r="AO76"/>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justice_Task_Force_Memeber</t>
+        </is>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76"/>
+      <c r="AS76"/>
+      <c r="AT76"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transform_phoenix</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectTransform</t>
-        </is>
-      </c>
+      <c r="A77"/>
+      <c r="B77"/>
       <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_KD</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77"/>
@@ -4847,21 +7082,36 @@
       <c r="AI77"/>
       <c r="AJ77"/>
       <c r="AK77"/>
+      <c r="AL77"/>
+      <c r="AM77"/>
+      <c r="AN77"/>
+      <c r="AO77"/>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaiser_PMC_Drone</t>
+        </is>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77"/>
+      <c r="AS77"/>
+      <c r="AT77"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unexhaust</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectExhaust</t>
-        </is>
-      </c>
+      <c r="A78"/>
+      <c r="B78"/>
       <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_PZ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
       <c r="F78"/>
       <c r="G78"/>
       <c r="H78"/>
@@ -4869,9 +7119,7 @@
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78"/>
-      <c r="M78" t="b">
-        <v>0</v>
-      </c>
+      <c r="M78"/>
       <c r="N78"/>
       <c r="O78"/>
       <c r="P78"/>
@@ -4896,21 +7144,36 @@
       <c r="AI78"/>
       <c r="AJ78"/>
       <c r="AK78"/>
+      <c r="AL78"/>
+      <c r="AM78"/>
+      <c r="AN78"/>
+      <c r="AO78"/>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan_Zzang</t>
+        </is>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78"/>
+      <c r="AS78"/>
+      <c r="AT78"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">use_PA_kotori</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_SSRFS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t xml:space="preserve">EffectUseCard</t>
         </is>
       </c>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
       <c r="F79"/>
       <c r="G79"/>
       <c r="H79"/>
@@ -4938,20 +7201,574 @@
       <c r="AD79"/>
       <c r="AE79"/>
       <c r="AF79"/>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
-        </is>
-      </c>
-      <c r="AH79" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG79"/>
+      <c r="AH79"/>
       <c r="AI79"/>
       <c r="AJ79"/>
       <c r="AK79"/>
+      <c r="AL79"/>
+      <c r="AM79"/>
+      <c r="AN79"/>
+      <c r="AO79"/>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall</t>
+        </is>
+      </c>
+      <c r="AQ79">
+        <v>0</v>
+      </c>
+      <c r="AR79"/>
+      <c r="AS79"/>
+      <c r="AT79"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_peroro</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+      <c r="N80"/>
+      <c r="O80"/>
+      <c r="P80"/>
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="S80"/>
+      <c r="T80"/>
+      <c r="U80"/>
+      <c r="V80"/>
+      <c r="W80"/>
+      <c r="X80"/>
+      <c r="Y80"/>
+      <c r="Z80"/>
+      <c r="AA80"/>
+      <c r="AB80"/>
+      <c r="AC80"/>
+      <c r="AD80"/>
+      <c r="AE80"/>
+      <c r="AF80"/>
+      <c r="AG80"/>
+      <c r="AH80"/>
+      <c r="AI80"/>
+      <c r="AJ80"/>
+      <c r="AK80"/>
+      <c r="AL80"/>
+      <c r="AM80"/>
+      <c r="AN80"/>
+      <c r="AO80"/>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peroro_Tlush</t>
+        </is>
+      </c>
+      <c r="AQ80">
+        <v>0</v>
+      </c>
+      <c r="AR80"/>
+      <c r="AS80"/>
+      <c r="AT80"/>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_sweeper</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
+      <c r="V81"/>
+      <c r="W81"/>
+      <c r="X81"/>
+      <c r="Y81"/>
+      <c r="Z81"/>
+      <c r="AA81"/>
+      <c r="AB81"/>
+      <c r="AC81"/>
+      <c r="AD81"/>
+      <c r="AE81"/>
+      <c r="AF81"/>
+      <c r="AG81"/>
+      <c r="AH81"/>
+      <c r="AI81"/>
+      <c r="AJ81"/>
+      <c r="AK81"/>
+      <c r="AL81"/>
+      <c r="AM81"/>
+      <c r="AN81"/>
+      <c r="AO81"/>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sweeper</t>
+        </is>
+      </c>
+      <c r="AQ81">
+        <v>0</v>
+      </c>
+      <c r="AR81"/>
+      <c r="AS81"/>
+      <c r="AT81"/>
+    </row>
+    <row r="82">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_sweeper_Tutorial</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+      <c r="U82"/>
+      <c r="V82"/>
+      <c r="W82"/>
+      <c r="X82"/>
+      <c r="Y82"/>
+      <c r="Z82"/>
+      <c r="AA82"/>
+      <c r="AB82"/>
+      <c r="AC82"/>
+      <c r="AD82"/>
+      <c r="AE82"/>
+      <c r="AF82"/>
+      <c r="AG82"/>
+      <c r="AH82"/>
+      <c r="AI82"/>
+      <c r="AJ82"/>
+      <c r="AK82"/>
+      <c r="AL82"/>
+      <c r="AM82"/>
+      <c r="AN82"/>
+      <c r="AO82"/>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sweeper_Tutorial</t>
+        </is>
+      </c>
+      <c r="AQ82">
+        <v>0</v>
+      </c>
+      <c r="AR82"/>
+      <c r="AS82"/>
+      <c r="AT82"/>
+    </row>
+    <row r="83">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_thundergun</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+      <c r="N83"/>
+      <c r="O83"/>
+      <c r="P83"/>
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="S83"/>
+      <c r="T83"/>
+      <c r="U83"/>
+      <c r="V83"/>
+      <c r="W83"/>
+      <c r="X83"/>
+      <c r="Y83"/>
+      <c r="Z83"/>
+      <c r="AA83"/>
+      <c r="AB83"/>
+      <c r="AC83"/>
+      <c r="AD83"/>
+      <c r="AE83"/>
+      <c r="AF83"/>
+      <c r="AG83"/>
+      <c r="AH83"/>
+      <c r="AI83"/>
+      <c r="AJ83"/>
+      <c r="AK83"/>
+      <c r="AL83"/>
+      <c r="AM83"/>
+      <c r="AN83"/>
+      <c r="AO83"/>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thundergun</t>
+        </is>
+      </c>
+      <c r="AQ83">
+        <v>0</v>
+      </c>
+      <c r="AR83"/>
+      <c r="AS83"/>
+      <c r="AT83"/>
+    </row>
+    <row r="84">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summon_thundergun_Tutorial</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
+      <c r="L84"/>
+      <c r="M84"/>
+      <c r="N84"/>
+      <c r="O84"/>
+      <c r="P84"/>
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="S84"/>
+      <c r="T84"/>
+      <c r="U84"/>
+      <c r="V84"/>
+      <c r="W84"/>
+      <c r="X84"/>
+      <c r="Y84"/>
+      <c r="Z84"/>
+      <c r="AA84"/>
+      <c r="AB84"/>
+      <c r="AC84"/>
+      <c r="AD84"/>
+      <c r="AE84"/>
+      <c r="AF84"/>
+      <c r="AG84"/>
+      <c r="AH84"/>
+      <c r="AI84"/>
+      <c r="AJ84"/>
+      <c r="AK84"/>
+      <c r="AL84"/>
+      <c r="AM84"/>
+      <c r="AN84"/>
+      <c r="AO84"/>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thundergun_Tutorial</t>
+        </is>
+      </c>
+      <c r="AQ84">
+        <v>0</v>
+      </c>
+      <c r="AR84"/>
+      <c r="AS84"/>
+      <c r="AT84"/>
+    </row>
+    <row r="85">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transform_fish</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTransform</t>
+        </is>
+      </c>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+      <c r="N85"/>
+      <c r="O85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+      <c r="U85"/>
+      <c r="V85"/>
+      <c r="W85"/>
+      <c r="X85"/>
+      <c r="Y85"/>
+      <c r="Z85"/>
+      <c r="AA85"/>
+      <c r="AB85"/>
+      <c r="AC85"/>
+      <c r="AD85"/>
+      <c r="AE85"/>
+      <c r="AF85"/>
+      <c r="AG85"/>
+      <c r="AH85"/>
+      <c r="AI85"/>
+      <c r="AJ85"/>
+      <c r="AK85"/>
+      <c r="AL85"/>
+      <c r="AM85"/>
+      <c r="AN85"/>
+      <c r="AO85"/>
+      <c r="AP85"/>
+      <c r="AQ85"/>
+      <c r="AR85"/>
+      <c r="AS85"/>
+      <c r="AT85"/>
+    </row>
+    <row r="86">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transform_phoenix</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectTransform</t>
+        </is>
+      </c>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+      <c r="M86"/>
+      <c r="N86"/>
+      <c r="O86"/>
+      <c r="P86"/>
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="S86"/>
+      <c r="T86"/>
+      <c r="U86"/>
+      <c r="V86"/>
+      <c r="W86"/>
+      <c r="X86"/>
+      <c r="Y86"/>
+      <c r="Z86"/>
+      <c r="AA86"/>
+      <c r="AB86"/>
+      <c r="AC86"/>
+      <c r="AD86"/>
+      <c r="AE86"/>
+      <c r="AF86"/>
+      <c r="AG86"/>
+      <c r="AH86"/>
+      <c r="AI86"/>
+      <c r="AJ86"/>
+      <c r="AK86"/>
+      <c r="AL86"/>
+      <c r="AM86"/>
+      <c r="AN86"/>
+      <c r="AO86"/>
+      <c r="AP86"/>
+      <c r="AQ86"/>
+      <c r="AR86"/>
+      <c r="AS86"/>
+      <c r="AT86"/>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unexhaust</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectExhaust</t>
+        </is>
+      </c>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="O87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87"/>
+      <c r="V87"/>
+      <c r="W87"/>
+      <c r="X87"/>
+      <c r="Y87"/>
+      <c r="Z87"/>
+      <c r="AA87"/>
+      <c r="AB87"/>
+      <c r="AC87"/>
+      <c r="AD87"/>
+      <c r="AE87"/>
+      <c r="AF87"/>
+      <c r="AG87"/>
+      <c r="AH87"/>
+      <c r="AI87"/>
+      <c r="AJ87"/>
+      <c r="AK87"/>
+      <c r="AL87"/>
+      <c r="AM87"/>
+      <c r="AN87"/>
+      <c r="AO87"/>
+      <c r="AP87"/>
+      <c r="AQ87"/>
+      <c r="AR87"/>
+      <c r="AS87"/>
+      <c r="AT87"/>
+    </row>
+    <row r="88">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">use_PA_kotori</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectUseCard</t>
+        </is>
+      </c>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="O88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+      <c r="U88"/>
+      <c r="V88"/>
+      <c r="W88"/>
+      <c r="X88"/>
+      <c r="Y88"/>
+      <c r="Z88"/>
+      <c r="AA88"/>
+      <c r="AB88"/>
+      <c r="AC88"/>
+      <c r="AD88"/>
+      <c r="AE88"/>
+      <c r="AF88"/>
+      <c r="AG88"/>
+      <c r="AH88"/>
+      <c r="AI88"/>
+      <c r="AJ88"/>
+      <c r="AK88"/>
+      <c r="AL88"/>
+      <c r="AM88"/>
+      <c r="AN88"/>
+      <c r="AO88"/>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
+        </is>
+      </c>
+      <c r="AQ88">
+        <v>0</v>
+      </c>
+      <c r="AR88"/>
+      <c r="AS88"/>
+      <c r="AT88"/>
+    </row>
+    <row r="89">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndTable</t>
         </is>
